--- a/任务级数据.xlsx
+++ b/任务级数据.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P99"/>
+  <dimension ref="A1:P108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>海康的同事没有驻场。垂直电镀vcp1自动化问题：小车出现平台失联、直接撞库（使用第一个货架），会突然间不动的现象</t>
+          <t>VCP1自动化问题（海康同事未驻场）：AGV小车出现平台失联、使用第一个货架时直接撞库，以及运行中突然停止不动等现象。</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>海康的同事没有驻场。垂直电镀vcp1自动化问题：小车出现平台失联、直接撞库（使用第一个货架），会突然间不动的现象</t>
+          <t>VCP1自动化问题（海康同事未驻场）：AGV小车出现平台失联、使用第一个货架时直接撞库，以及运行中突然停止不动等现象。</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>海康的同事没有驻场。 垂直电镀vcp1自动化问题：1、AGV老是撞货架（使用第一个货架） 2、agv路线不对（应该去放板机，结果跑去收板机） 3、存在识别不到载具的情况</t>
+          <t>VCP1自动化问题（海康同事未驻场）：① AGV频繁撞上第一个货架；② AGV路线错误，应去放板机却前往收板机；③ 存在无法识别载具的情况。</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>海康的同事没有驻场。垂直电镀vcp1自动化问题：AGV倒车入第一个货架的位置不对，无法入库，改为使用第二个货架正常运行，第一个货架撞库问题尚未解决</t>
+          <t>VCP1自动化问题（海康同事未驻场）：AGV倒车进入第一个货架时定位不准，无法入库；改用第二个货架后可正常运行，第一个货架撞库问题尚未解决。</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>海康的同事没有驻场。垂直电镀vcp1自动化问题：AGV倒车入第一个货架的位置不对，无法入库，改为使用第二个货架正常运行，第一个货架撞库问题尚未解决</t>
+          <t>VCP1自动化问题（海康同事未驻场）：AGV倒车进入第一个货架时定位不准，无法入库；改用第二个货架后可正常运行，第一个货架撞库问题尚未解决。</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>海康的同事下午才开始驻场。垂直电镀vcp1自动化问题：1、小车进入放板机与设备的升降零件发生剐蹭（光栅铁片扭曲），导致AGV小车掉漆，证实是光栅铁片高度问题 2、退空载时，倒车入点位的位置不对（底码位置有误），无法进入放板机2号工位。3、退空载回去的路线也不对，海康库位编码需要更新，导致小车退空载路线不正确</t>
+          <t>VCP1自动化问题（海康同事下午才到场）：① 小车进入放板机时与设备升降零件发生剐蹭，导致光栅铁片扭曲、AGV掉漆，已确认为光栅铁片高度问题；② 退空载时倒车入点位位置错误（底码位置有误），无法进入放板机2号工位；③ 退空载返回路线错误，需更新海康库位编码，导致小车退空载路径不正确。</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6600,6 +6600,635 @@
       </c>
       <c r="P99" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>T00099</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>垂直电镀VCP2自动化测试（40%）</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>MSAP</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>VCP2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>VCP1：早上设备在生产暂停自动化测试。主线设备未接收PDA配方下发指令，需联系RMS及设备厂商排查。
+VCP2：① 早上进行自动化测试时发现：RMS未维护VCP2主线配方（invoke接口数据缺失）；② PDA配方下发时设备回复S6F11超时，需联系设备厂商核对，下午设备在生产暂停自动化测试。
+VCP线整体：下午4点半因甲方经理前来验收，暂停所有测试。
+PLB： 现场无正式工单，使用测试工单测试，但主线设备未维护对应的料号与Lot，导致无法下发。</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>胜宏科技HDI二处工业物联网平台实施项目2026</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>20</v>
+      </c>
+      <c r="N100" t="b">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.1814768460575719</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>T00100</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VCP1线PDA配方下发问题排查（100%）</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>MSAP</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>VCP1</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>VCP1：早上设备在生产暂停自动化测试。主线设备未接收PDA配方下发指令，需联系RMS及设备厂商排查。
+VCP2：① 早上进行自动化测试时发现：RMS未维护VCP2主线配方（invoke接口数据缺失）；② PDA配方下发时设备回复S6F11超时，需联系设备厂商核对，下午设备在生产暂停自动化测试。
+VCP线整体：下午4点半因甲方经理前来验收，暂停所有测试。
+PLB： 现场无正式工单，使用测试工单测试，但主线设备未维护对应的料号与Lot，导致无法下发。</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>胜宏科技HDI二处工业物联网平台实施项目2026</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>20</v>
+      </c>
+      <c r="N101" t="b">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.2728410513141427</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>T00101</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VCP2线PDA配方下发问题排查（70%）</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>MSAP</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>VCP2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>VCP1：早上设备在生产暂停自动化测试。主线设备未接收PDA配方下发指令，需联系RMS及设备厂商排查。
+VCP2：① 早上进行自动化测试时发现：RMS未维护VCP2主线配方（invoke接口数据缺失）；② PDA配方下发时设备回复S6F11超时，需联系设备厂商核对，下午设备在生产暂停自动化测试。
+VCP线整体：下午4点半因甲方经理前来验收，暂停所有测试。
+PLB： 现场无正式工单，使用测试工单测试，但主线设备未维护对应的料号与Lot，导致无法下发。</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>胜宏科技HDI二处工业物联网平台实施项目2026</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>20</v>
+      </c>
+      <c r="N102" t="b">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.2728410513141427</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>T00102</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PLB线PDA配方下发问题排查（50%）</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>MSAP</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>安美特PLB</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>VCP1：早上设备在生产暂停自动化测试。主线设备未接收PDA配方下发指令，需联系RMS及设备厂商排查。
+VCP2：① 早上进行自动化测试时发现：RMS未维护VCP2主线配方（invoke接口数据缺失）；② PDA配方下发时设备回复S6F11超时，需联系设备厂商核对，下午设备在生产暂停自动化测试。
+VCP线整体：下午4点半因甲方经理前来验收，暂停所有测试。
+PLB： 现场无正式工单，使用测试工单测试，但主线设备未维护对应的料号与Lot，导致无法下发。</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>胜宏科技HDI二处工业物联网平台实施项目2026</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>20</v>
+      </c>
+      <c r="N103" t="b">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.2728410513141427</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>T00103</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>垂直电镀VCP2自动化测试（70%）</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>MSAP</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>VCP2</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1、agv小车经常与平台失联
+2、vcp2线设备没有自动切换在线模式（待找厂商确认）
+3、VCP2线PDA配方下发失败，pda接口，rms返回数据缺少配方id（有待验证）
+4、VCP2工作流放板机工位一的载具编码未写入点位（待验证）
+5、plb、vcp1没有工单无法测pda下发（vcp1设备在维护）</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>胜宏科技HDI二处工业物联网平台实施项目2026</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>20</v>
+      </c>
+      <c r="N104" t="b">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>8</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>T00104</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VCP2线PDA配方下发问题排查（90%）</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>MSAP</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>VCP2</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1、agv小车经常与平台失联
+2、vcp2线设备没有自动切换在线模式（待找厂商确认）
+3、VCP2线PDA配方下发失败，pda接口，rms返回数据缺少配方id（有待验证）
+4、VCP2工作流放板机工位一的载具编码未写入点位（待验证）
+5、plb、vcp1没有工单无法测pda下发（vcp1设备在维护）</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>胜宏科技HDI二处工业物联网平台实施项目2026</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>20</v>
+      </c>
+      <c r="N105" t="b">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>8</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>T00105</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>垂直电镀VCP2自动化测试（80%）</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>MSAP</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>VCP2</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>投收板机：VCP1，配方下发后设备没有请求放板，收板机二号工位载具编码为空（下周一找设备排查）
+自动化物流（海康）：小车与平台经常失联严重（一整天高频率间歇性/长期性失联）
+软件集成（SIE）：VCP1自动化叫料接口报错mes获取任务lot与载具绑定不正确（延误时间2小时，已解决）
+生产/工艺：三条线都是因为设备没有维护对应lot、料号导致pda下发不到设备（原因是生产没有配置正确lot和料号，以及使用工单错误——使用转场工单）
+维护：plb在保养维护，无法自动化测试
+待办项：VCP2线小车调用Eap的工作流TackComplete接口后，收板机1号工位载具编码没有写入值（正在排查）</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>胜宏科技HDI二处工业物联网平台实施项目2026</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>20</v>
+      </c>
+      <c r="N106" t="b">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>8</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>T00106</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>PLB线PDA配方下发问题排查（设备没有维护对应lto、料号导致）（100%）</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>MSAP</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>安美特PLB</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>3</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>投收板机：VCP1，配方下发后设备没有请求放板，收板机二号工位载具编码为空（下周一找设备排查）
+自动化物流（海康）：小车与平台经常失联严重（一整天高频率间歇性/长期性失联）
+软件集成（SIE）：VCP1自动化叫料接口报错mes获取任务lot与载具绑定不正确（延误时间2小时，已解决）
+生产/工艺：三条线都是因为设备没有维护对应lot、料号导致pda下发不到设备（原因是生产没有配置正确lot和料号，以及使用工单错误——使用转场工单）
+维护：plb在保养维护，无法自动化测试
+待办项：VCP2线小车调用Eap的工作流TackComplete接口后，收板机1号工位载具编码没有写入值（正在排查）</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>胜宏科技HDI二处工业物联网平台实施项目2026</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>20</v>
+      </c>
+      <c r="N107" t="b">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>8</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>T00107</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VCP2线PDA配方下发问题排查（设备没有维护对应料号导致）（100%）</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>MSAP</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>VCP2</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>调试</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>3</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>投收板机：VCP1，配方下发后设备没有请求放板，收板机二号工位载具编码为空（下周一找设备排查）
+自动化物流（海康）：小车与平台经常失联严重（一整天高频率间歇性/长期性失联）
+软件集成（SIE）：VCP1自动化叫料接口报错mes获取任务lot与载具绑定不正确（延误时间2小时，已解决）
+生产/工艺：三条线都是因为设备没有维护对应lot、料号导致pda下发不到设备（原因是生产没有配置正确lot和料号，以及使用工单错误——使用转场工单）
+维护：plb在保养维护，无法自动化测试
+待办项：VCP2线小车调用Eap的工作流TackComplete接口后，收板机1号工位载具编码没有写入值（正在排查）</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>胜宏科技HDI二处工业物联网平台实施项目2026</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>20</v>
+      </c>
+      <c r="N108" t="b">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>8</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.375</v>
       </c>
     </row>
   </sheetData>
